--- a/public/sample_team_import.xlsx
+++ b/public/sample_team_import.xlsx
@@ -397,11 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:F8"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,6 +417,15 @@
       <c r="C1" t="str">
         <v>役割</v>
       </c>
+      <c r="D1" t="str">
+        <v>表示名</v>
+      </c>
+      <c r="E1" t="str">
+        <v>メール</v>
+      </c>
+      <c r="F1" t="str">
+        <v>初期パスワード</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -425,6 +437,15 @@
       <c r="C2" t="str">
         <v/>
       </c>
+      <c r="D2" t="str">
+        <v>山田 太郎</v>
+      </c>
+      <c r="E2" t="str">
+        <v>yamada@example.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Pass1234</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -436,6 +457,15 @@
       <c r="C3" t="str">
         <v>サブリーダー</v>
       </c>
+      <c r="D3" t="str">
+        <v>鈴木 花子</v>
+      </c>
+      <c r="E3" t="str">
+        <v>suzuki@example.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -447,6 +477,15 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>田中 一郎</v>
+      </c>
+      <c r="E4" t="str">
+        <v>tanaka@example.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -458,6 +497,15 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>佐藤 二郎</v>
+      </c>
+      <c r="E5" t="str">
+        <v>sato@example.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -469,6 +517,15 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v>伊藤 三郎</v>
+      </c>
+      <c r="E6" t="str">
+        <v>ito@example.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -480,6 +537,15 @@
       <c r="C7" t="str">
         <v>リーダー</v>
       </c>
+      <c r="D7" t="str">
+        <v>渡辺 四郎</v>
+      </c>
+      <c r="E7" t="str">
+        <v>watanabe@example.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -491,10 +557,19 @@
       <c r="C8" t="str">
         <v/>
       </c>
+      <c r="D8" t="str">
+        <v>小林 五郎</v>
+      </c>
+      <c r="E8" t="str">
+        <v>kobayashi@example.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>